--- a/dist/downloads/货价监控指标-26.08.02.xlsx
+++ b/dist/downloads/货价监控指标-26.08.02.xlsx
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:CA200"/>
+  <dimension ref="B1:CA176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.66" customWidth="1" style="75" min="1" max="1"/>
@@ -3297,7 +3297,6 @@
       <c r="J40" s="95" t="n"/>
       <c r="K40" s="79" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42" ht="13.5" customHeight="1" s="76">
       <c r="B42" s="77" t="inlineStr">
         <is>
@@ -3767,7 +3766,6 @@
       </c>
       <c r="P52" s="79" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54" ht="13.5" customHeight="1" s="76">
       <c r="B54" s="77" t="inlineStr">
         <is>
@@ -4285,13 +4283,11 @@
         <f>AVERAGE(C46,N57,Y57,AJ57,AU57,BF57,BQ57)</f>
         <v/>
       </c>
-      <c r="D57" s="104">
-        <f>IF((J57/(-2)*40+60)&gt;120,120,IF(J57&gt;0,0,(J57/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E57" s="104">
-        <f>IFERROR(IF((M57/(-2)*40+60)&gt;120,120,IF(M57&gt;0,0,(M57/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D57" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="104" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="84">
         <f>SUM(U57,AF57,AQ57,BB57,BM57,BX57)/SUM(U57:V57,AF57:AG57,AQ57:AR57,BB57:BC57,BM57:BN57,BX57:BY57)</f>
@@ -4309,9 +4305,8 @@
         <f>AVERAGE(I46-2%,P57-2%,AA57-2%,AL57-2%,AW57-2%,BH57-2%,BS57-2%)</f>
         <v/>
       </c>
-      <c r="J57" s="84">
-        <f>(H57-I57)*100</f>
-        <v/>
+      <c r="J57" s="84" t="n">
+        <v>1.3102</v>
       </c>
       <c r="K57" s="84">
         <f>IFERROR(AVERAGE(L46,R57,AC57,AN57,AY57,BJ57,BU57),"(NULL)")</f>
@@ -4321,10 +4316,7 @@
         <f>AVERAGE(M46-2%,S57-2%,AD57-2%,AO57-2%,AZ57-2%,BK57-2%,BV57-2%)</f>
         <v/>
       </c>
-      <c r="M57" s="84">
-        <f>IFERROR(((K57-L57)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M57" s="84" t="n"/>
       <c r="N57" s="103" t="n">
         <v>71.8851437589701</v>
       </c>
@@ -4538,13 +4530,11 @@
         <f>AVERAGE(C47,N58,Y58,AJ58,AU58,BF58,BQ58)</f>
         <v/>
       </c>
-      <c r="D58" s="104">
-        <f>IF((J58/(-2)*40+60)&gt;120,120,IF(J58&gt;0,0,(J58/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E58" s="104">
-        <f>IFERROR(IF((M58/(-2)*40+60)&gt;120,120,IF(M58&gt;0,0,(M58/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D58" s="104" t="n">
+        <v>94.22</v>
+      </c>
+      <c r="E58" s="104" t="n">
+        <v>120</v>
       </c>
       <c r="F58" s="84">
         <f>SUM(U58,AF58,AQ58,BB58,BM58,BX58)/SUM(U58:V58,AF58:AG58,AQ58:AR58,BB58:BC58,BM58:BN58,BX58:BY58)</f>
@@ -4562,9 +4552,8 @@
         <f>AVERAGE(I47-2%,P58-2%,AA58-2%,AL58-2%,AW58-2%,BH58-2%,BS58-2%)</f>
         <v/>
       </c>
-      <c r="J58" s="84">
-        <f>(H58-I58)*100</f>
-        <v/>
+      <c r="J58" s="84" t="n">
+        <v>-1.7109</v>
       </c>
       <c r="K58" s="84">
         <f>IFERROR(AVERAGE(L47,R58,AC58,AN58,AY58,BJ58,BU58),"(NULL)")</f>
@@ -4574,10 +4563,7 @@
         <f>AVERAGE(M47-2%,S58-2%,AD58-2%,AO58-2%,AZ58-2%,BK58-2%,BV58-2%)</f>
         <v/>
       </c>
-      <c r="M58" s="84">
-        <f>IFERROR(((K58-L58)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M58" s="84" t="n"/>
       <c r="N58" s="103" t="n">
         <v>119.335376267249</v>
       </c>
@@ -4791,13 +4777,11 @@
         <f>AVERAGE(C48,N59,Y59,AJ59,AU59,BF59,BQ59)</f>
         <v/>
       </c>
-      <c r="D59" s="104">
-        <f>IF((J59/(-2)*40+60)&gt;120,120,IF(J59&gt;0,0,(J59/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E59" s="104">
-        <f>IFERROR(IF((M59/(-2)*40+60)&gt;120,120,IF(M59&gt;0,0,(M59/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D59" s="104" t="n">
+        <v>119.64</v>
+      </c>
+      <c r="E59" s="104" t="n">
+        <v>120</v>
       </c>
       <c r="F59" s="84">
         <f>SUM(U59,AF59,AQ59,BB59,BM59,BX59)/SUM(U59:V59,AF59:AG59,AQ59:AR59,BB59:BC59,BM59:BN59,BX59:BY59)</f>
@@ -4815,9 +4799,8 @@
         <f>AVERAGE(I48-2%,P59-2%,AA59-2%,AL59-2%,AW59-2%,BH59-2%,BS59-2%)</f>
         <v/>
       </c>
-      <c r="J59" s="84">
-        <f>(H59-I59)*100</f>
-        <v/>
+      <c r="J59" s="84" t="n">
+        <v>-2.9819</v>
       </c>
       <c r="K59" s="84">
         <f>IFERROR(AVERAGE(L48,R59,AC59,AN59,AY59,BJ59,BU59),"(NULL)")</f>
@@ -4827,10 +4810,7 @@
         <f>AVERAGE(M48-2%,S59-2%,AD59-2%,AO59-2%,AZ59-2%,BK59-2%,BV59-2%)</f>
         <v/>
       </c>
-      <c r="M59" s="84">
-        <f>IFERROR(((K59-L59)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M59" s="84" t="n"/>
       <c r="N59" s="103" t="n">
         <v>120</v>
       </c>
@@ -5044,13 +5024,11 @@
         <f>AVERAGE(C49,N60,Y60,AJ60,AU60,BF60,BQ60)</f>
         <v/>
       </c>
-      <c r="D60" s="104">
-        <f>IF((J60/(-2)*40+60)&gt;120,120,IF(J60&gt;0,0,(J60/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E60" s="104">
-        <f>IFERROR(IF((M60/(-2)*40+60)&gt;120,120,IF(M60&gt;0,0,(M60/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D60" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="104" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="84">
         <f>SUM(U60,AF60,AQ60,BB60,BM60,BX60)/SUM(U60:V60,AF60:AG60,AQ60:AR60,BB60:BC60,BM60:BN60,BX60:BY60)</f>
@@ -5068,9 +5046,8 @@
         <f>AVERAGE(I49-2%,P60-2%,AA60-2%,AL60-2%,AW60-2%,BH60-2%,BS60-2%)</f>
         <v/>
       </c>
-      <c r="J60" s="84">
-        <f>(H60-I60)*100</f>
-        <v/>
+      <c r="J60" s="84" t="n">
+        <v>0.8898</v>
       </c>
       <c r="K60" s="84">
         <f>IFERROR(AVERAGE(L49,R60,AC60,AN60,AY60,BJ60,BU60),"(NULL)")</f>
@@ -5080,10 +5057,7 @@
         <f>AVERAGE(M49-2%,S60-2%,AD60-2%,AO60-2%,AZ60-2%,BK60-2%,BV60-2%)</f>
         <v/>
       </c>
-      <c r="M60" s="84">
-        <f>IFERROR(((K60-L60)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M60" s="84" t="n"/>
       <c r="N60" s="103" t="n">
         <v>0</v>
       </c>
@@ -5297,13 +5271,11 @@
         <f>AVERAGE(C50,N61,Y61,AJ61,AU61,BF61,BQ61)</f>
         <v/>
       </c>
-      <c r="D61" s="104">
-        <f>IF((J61/(-2)*40+60)&gt;120,120,IF(J61&gt;0,0,(J61/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E61" s="104">
-        <f>IFERROR(IF((M61/(-2)*40+60)&gt;120,120,IF(M61&gt;0,0,(M61/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D61" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="104" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="84">
         <f>SUM(U61,AF61,AQ61,BB61,BM61,BX61)/SUM(U61:V61,AF61:AG61,AQ61:AR61,BB61:BC61,BM61:BN61,BX61:BY61)</f>
@@ -5321,9 +5293,8 @@
         <f>AVERAGE(I50-2%,P61-2%,AA61-2%,AL61-2%,AW61-2%,BH61-2%,BS61-2%)</f>
         <v/>
       </c>
-      <c r="J61" s="84">
-        <f>(H61-I61)*100</f>
-        <v/>
+      <c r="J61" s="84" t="n">
+        <v>7.1327</v>
       </c>
       <c r="K61" s="84">
         <f>IFERROR(AVERAGE(L50,R61,AC61,AN61,AY61,BJ61,BU61),"(NULL)")</f>
@@ -5333,10 +5304,7 @@
         <f>AVERAGE(M50-2%,S61-2%,AD61-2%,AO61-2%,AZ61-2%,BK61-2%,BV61-2%)</f>
         <v/>
       </c>
-      <c r="M61" s="84">
-        <f>IFERROR(((K61-L61)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M61" s="84" t="n"/>
       <c r="N61" s="103" t="n">
         <v>11.4174663533469</v>
       </c>
@@ -5550,13 +5518,11 @@
         <f>AVERAGE(C51,N62,Y62,AJ62,AU62,BF62,BQ62)</f>
         <v/>
       </c>
-      <c r="D62" s="104">
-        <f>IF((J62/(-2)*40+60)&gt;120,120,IF(J62&gt;0,0,(J62/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E62" s="104">
-        <f>IFERROR(IF((M62/(-2)*40+60)&gt;120,120,IF(M62&gt;0,0,(M62/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D62" s="104" t="n">
+        <v>120</v>
+      </c>
+      <c r="E62" s="104" t="n">
+        <v>120</v>
       </c>
       <c r="F62" s="84">
         <f>SUM(U62,AF62,AQ62,BB62,BM62,BX62)/SUM(U62:V62,AF62:AG62,AQ62:AR62,BB62:BC62,BM62:BN62,BX62:BY62)</f>
@@ -5574,9 +5540,8 @@
         <f>AVERAGE(I51-2%,P62-2%,AA62-2%,AL62-2%,AW62-2%,BH62-2%,BS62-2%)</f>
         <v/>
       </c>
-      <c r="J62" s="84">
-        <f>(H62-I62)*100</f>
-        <v/>
+      <c r="J62" s="84" t="n">
+        <v>-13.989</v>
       </c>
       <c r="K62" s="84">
         <f>IFERROR(AVERAGE(L51,R62,AC62,AN62,AY62,BJ62,BU62),"(NULL)")</f>
@@ -5586,10 +5551,7 @@
         <f>AVERAGE(M51-2%,S62-2%,AD62-2%,AO62-2%,AZ62-2%,BK62-2%,BV62-2%)</f>
         <v/>
       </c>
-      <c r="M62" s="84">
-        <f>IFERROR(((K62-L62)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M62" s="84" t="n"/>
       <c r="N62" s="103" t="n">
         <v>61.801667164079</v>
       </c>
@@ -5827,13 +5789,11 @@
         <f>AVERAGE(C52,N63,Y63,AJ63,AU63,BF63,BQ63)</f>
         <v/>
       </c>
-      <c r="D63" s="104">
-        <f>IF((J63/(-2)*40+60)&gt;120,120,IF(J63&gt;0,0,(J63/(-2)*40+60)))</f>
-        <v/>
-      </c>
-      <c r="E63" s="104">
-        <f>IFERROR(IF((M63/(-2)*40+60)&gt;120,120,IF(M63&gt;0,0,(M63/(-2)*40+60))),"(NULL)")</f>
-        <v/>
+      <c r="D63" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="104" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="84">
         <f>SUM(U63,AF63,AQ63,BB63,BM63,BX63)/SUM(U63:V63,AF63:AG63,AQ63:AR63,BB63:BC63,BM63:BN63,BX63:BY63)</f>
@@ -5851,9 +5811,8 @@
         <f>AVERAGE(I52-2%,P63-2%,AA63-2%,AL63-2%,AW63-2%,BH63-2%,BS63-2%)</f>
         <v/>
       </c>
-      <c r="J63" s="84">
-        <f>(H63-I63)*100</f>
-        <v/>
+      <c r="J63" s="84" t="n">
+        <v>1.649</v>
       </c>
       <c r="K63" s="84">
         <f>IFERROR(AVERAGE(L52,R63,AC63,AN63,AY63,BJ63,BU63),"(NULL)")</f>
@@ -5863,10 +5822,7 @@
         <f>AVERAGE(M52-2%,S63-2%,AD63-2%,AO63-2%,AZ63-2%,BK63-2%,BV63-2%)</f>
         <v/>
       </c>
-      <c r="M63" s="84">
-        <f>IFERROR(((K63-L63)*100),"(NULL)")</f>
-        <v/>
-      </c>
+      <c r="M63" s="84" t="n"/>
       <c r="N63" s="103" t="n">
         <v>0</v>
       </c>
@@ -6905,8 +6861,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77"/>
     <row r="78" ht="13.5" customHeight="1" s="76">
       <c r="B78" s="77" t="inlineStr">
         <is>
@@ -7397,8 +7351,6 @@
         <v/>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90" ht="13.5" customHeight="1" s="76">
       <c r="B90" s="77" t="inlineStr">
         <is>
@@ -8779,8 +8731,6 @@
         <v/>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112"/>
     <row r="113" ht="13.5" customHeight="1" s="76">
       <c r="B113" s="77" t="inlineStr">
         <is>
@@ -8976,7 +8926,6 @@
         <v/>
       </c>
     </row>
-    <row r="120"/>
     <row r="121" ht="13.5" customHeight="1" s="76">
       <c r="B121" s="77" t="inlineStr">
         <is>
@@ -9761,7 +9710,6 @@
         <v/>
       </c>
     </row>
-    <row r="128"/>
     <row r="129" ht="13.5" customHeight="1" s="76">
       <c r="B129" s="77" t="inlineStr">
         <is>
@@ -9955,7 +9903,6 @@
         <v/>
       </c>
     </row>
-    <row r="136"/>
     <row r="137" ht="13.5" customHeight="1" s="76">
       <c r="B137" s="77" t="inlineStr">
         <is>
@@ -10360,7 +10307,6 @@
         <v>464967.75598</v>
       </c>
     </row>
-    <row r="151"/>
     <row r="152" ht="13.5" customHeight="1" s="76">
       <c r="B152" s="77" t="inlineStr">
         <is>
@@ -11315,30 +11261,6 @@
       <c r="W176" s="95" t="n"/>
       <c r="X176" s="95" t="n"/>
     </row>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
   </sheetData>
   <mergeCells count="65">
     <mergeCell ref="B122:B123"/>

--- a/dist/downloads/货价监控指标-26.08.02.xlsx
+++ b/dist/downloads/货价监控指标-26.08.02.xlsx
@@ -3297,6 +3297,7 @@
       <c r="J40" s="95" t="n"/>
       <c r="K40" s="79" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="13.5" customHeight="1" s="76">
       <c r="B42" s="77" t="inlineStr">
         <is>
@@ -3385,14 +3386,12 @@
       </c>
       <c r="J45" s="101" t="inlineStr">
         <is>
-          <t>完成差值
-（pp）</t>
+          <t>本月目标</t>
         </is>
       </c>
       <c r="K45" s="101" t="inlineStr">
         <is>
-          <t>差值目标
-（pp）</t>
+          <t>完成差值 （pp）</t>
         </is>
       </c>
       <c r="L45" s="100" t="inlineStr">
@@ -3407,14 +3406,12 @@
       </c>
       <c r="N45" s="102" t="inlineStr">
         <is>
-          <t>完成差值
-（pp）</t>
+          <t>本月目标</t>
         </is>
       </c>
       <c r="O45" s="102" t="inlineStr">
         <is>
-          <t>差值目标
-（pp）</t>
+          <t>完成差值 （pp）</t>
         </is>
       </c>
       <c r="P45" s="79" t="n"/>
@@ -3447,10 +3444,10 @@
         <v>0.7837468839</v>
       </c>
       <c r="J46" s="84" t="n">
-        <v>0.3583</v>
+        <v>0.763747</v>
       </c>
       <c r="K46" s="105" t="n">
-        <v>0.763747</v>
+        <v>2.3583</v>
       </c>
       <c r="L46" s="84" t="n">
         <v>0.997261</v>
@@ -3459,10 +3456,10 @@
         <v>0.7837468839</v>
       </c>
       <c r="N46" s="84" t="n">
-        <v>21.3514</v>
+        <v>0.794747</v>
       </c>
       <c r="O46" s="84" t="n">
-        <v>0.794747</v>
+        <v>20.2514</v>
       </c>
       <c r="P46" s="79" t="n"/>
     </row>
@@ -3494,10 +3491,10 @@
         <v>0.8222685021</v>
       </c>
       <c r="J47" s="84" t="n">
-        <v>1.81</v>
+        <v>0.802269</v>
       </c>
       <c r="K47" s="105" t="n">
-        <v>0.802269</v>
+        <v>3.81</v>
       </c>
       <c r="L47" s="84" t="n">
         <v>0.733617</v>
@@ -3506,10 +3503,10 @@
         <v>0.8222685021</v>
       </c>
       <c r="N47" s="84" t="n">
-        <v>-8.8652</v>
+        <v>0.833269</v>
       </c>
       <c r="O47" s="84" t="n">
-        <v>0.833269</v>
+        <v>-9.965199999999999</v>
       </c>
       <c r="P47" s="79" t="n"/>
     </row>
@@ -3541,10 +3538,10 @@
         <v>0.7569341493</v>
       </c>
       <c r="J48" s="84" t="n">
-        <v>-8.0031</v>
+        <v>0.736934</v>
       </c>
       <c r="K48" s="105" t="n">
-        <v>0.736934</v>
+        <v>-6.0031</v>
       </c>
       <c r="L48" s="84" t="n">
         <v>0.692587</v>
@@ -3553,10 +3550,10 @@
         <v>0.7569341493</v>
       </c>
       <c r="N48" s="84" t="n">
-        <v>-6.4347</v>
+        <v>0.767934</v>
       </c>
       <c r="O48" s="84" t="n">
-        <v>0.767934</v>
+        <v>-7.5347</v>
       </c>
       <c r="P48" s="79" t="n"/>
     </row>
@@ -3588,10 +3585,10 @@
         <v>0.8296309959</v>
       </c>
       <c r="J49" s="84" t="n">
-        <v>-2.7947</v>
+        <v>0.809631</v>
       </c>
       <c r="K49" s="105" t="n">
-        <v>0.809631</v>
+        <v>-0.7947</v>
       </c>
       <c r="L49" s="84" t="n">
         <v>0.858967</v>
@@ -3600,10 +3597,10 @@
         <v>0.8296309959</v>
       </c>
       <c r="N49" s="84" t="n">
-        <v>2.9336</v>
+        <v>0.840631</v>
       </c>
       <c r="O49" s="84" t="n">
-        <v>0.840631</v>
+        <v>1.8336</v>
       </c>
       <c r="P49" s="79" t="n"/>
     </row>
@@ -3635,10 +3632,10 @@
         <v>0.8478180047</v>
       </c>
       <c r="J50" s="84" t="n">
-        <v>3.6969</v>
+        <v>0.8278180000000001</v>
       </c>
       <c r="K50" s="105" t="n">
-        <v>0.8278180000000001</v>
+        <v>5.6969</v>
       </c>
       <c r="L50" s="84" t="n">
         <v>0.882791</v>
@@ -3647,10 +3644,10 @@
         <v>0.8478180047</v>
       </c>
       <c r="N50" s="84" t="n">
-        <v>3.4973</v>
+        <v>0.858818</v>
       </c>
       <c r="O50" s="84" t="n">
-        <v>0.858818</v>
+        <v>2.3973</v>
       </c>
       <c r="P50" s="79" t="n"/>
     </row>
@@ -3693,13 +3690,13 @@
       <c r="I51" s="84" t="n">
         <v>0.8427285638999999</v>
       </c>
-      <c r="J51" s="84" t="inlineStr">
+      <c r="J51" s="84" t="n">
+        <v>0.822729</v>
+      </c>
+      <c r="K51" s="105" t="inlineStr">
         <is>
           <t>(NULL)</t>
         </is>
-      </c>
-      <c r="K51" s="105" t="n">
-        <v>0.822729</v>
       </c>
       <c r="L51" s="84" t="inlineStr">
         <is>
@@ -3709,13 +3706,13 @@
       <c r="M51" s="84" t="n">
         <v>0.8427285638999999</v>
       </c>
-      <c r="N51" s="84" t="inlineStr">
+      <c r="N51" s="84" t="n">
+        <v>0.853729</v>
+      </c>
+      <c r="O51" s="84" t="inlineStr">
         <is>
           <t>(NULL)</t>
         </is>
-      </c>
-      <c r="O51" s="84" t="n">
-        <v>0.853729</v>
       </c>
       <c r="P51" s="79" t="n"/>
     </row>
@@ -3747,10 +3744,10 @@
         <v>0.8188735651</v>
       </c>
       <c r="J52" s="84" t="n">
-        <v>-2.1876</v>
+        <v>0.798874</v>
       </c>
       <c r="K52" s="105" t="n">
-        <v>0.798874</v>
+        <v>-0.1876</v>
       </c>
       <c r="L52" s="84" t="n">
         <v>0.855483</v>
@@ -3759,13 +3756,14 @@
         <v>0.8188735651</v>
       </c>
       <c r="N52" s="84" t="n">
-        <v>3.6609</v>
+        <v>0.829874</v>
       </c>
       <c r="O52" s="84" t="n">
-        <v>0.829874</v>
+        <v>2.5609</v>
       </c>
       <c r="P52" s="79" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54" ht="13.5" customHeight="1" s="76">
       <c r="B54" s="77" t="inlineStr">
         <is>
